--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/66.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/66.xlsx
@@ -426,13 +426,13 @@
         <v>-4.999318215406853</v>
       </c>
       <c r="E2">
-        <v>-13.79250600044645</v>
+        <v>-15.35992380122541</v>
       </c>
       <c r="F2">
-        <v>-1.727885914175177</v>
+        <v>-2.600006026455747</v>
       </c>
       <c r="G2">
-        <v>-6.786934172174768</v>
+        <v>-5.786958946652784</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-4.328360115085196</v>
       </c>
       <c r="E3">
-        <v>-13.32389916666604</v>
+        <v>-16.3317254126994</v>
       </c>
       <c r="F3">
-        <v>-1.742664817008523</v>
+        <v>-2.408793150500134</v>
       </c>
       <c r="G3">
-        <v>-6.249522841072463</v>
+        <v>-5.426937267538262</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-3.782873791641845</v>
       </c>
       <c r="E4">
-        <v>-15.73356330485229</v>
+        <v>-15.876786797389</v>
       </c>
       <c r="F4">
-        <v>-1.770748957065635</v>
+        <v>-2.468840675161668</v>
       </c>
       <c r="G4">
-        <v>-4.749375945295814</v>
+        <v>-4.902057510473301</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-3.450196234189434</v>
       </c>
       <c r="E5">
-        <v>-14.8601014311276</v>
+        <v>-16.08269470845135</v>
       </c>
       <c r="F5">
-        <v>-1.471241125439834</v>
+        <v>-2.626364677212827</v>
       </c>
       <c r="G5">
-        <v>-4.400630072070309</v>
+        <v>-4.691367811225867</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-3.30543369027049</v>
       </c>
       <c r="E6">
-        <v>-16.02639377573198</v>
+        <v>-16.40354689613966</v>
       </c>
       <c r="F6">
-        <v>-1.492646967495576</v>
+        <v>-2.327080504785783</v>
       </c>
       <c r="G6">
-        <v>-3.636149230155926</v>
+        <v>-3.242576872301007</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-3.338817588756792</v>
       </c>
       <c r="E7">
-        <v>-16.62612579745986</v>
+        <v>-17.30400464347573</v>
       </c>
       <c r="F7">
-        <v>-1.864127500913612</v>
+        <v>-2.730318159324943</v>
       </c>
       <c r="G7">
-        <v>-3.615096185773189</v>
+        <v>-3.265875157032102</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-3.515499085080596</v>
       </c>
       <c r="E8">
-        <v>-15.68597996270373</v>
+        <v>-17.14553471216557</v>
       </c>
       <c r="F8">
-        <v>-1.659867838363907</v>
+        <v>-2.299855381725374</v>
       </c>
       <c r="G8">
-        <v>-2.545920564119156</v>
+        <v>-2.769379415161724</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-3.79716127950844</v>
       </c>
       <c r="E9">
-        <v>-15.15702696837356</v>
+        <v>-17.49928033354652</v>
       </c>
       <c r="F9">
-        <v>-1.745577356796766</v>
+        <v>-2.593388199274782</v>
       </c>
       <c r="G9">
-        <v>-2.891183704060114</v>
+        <v>-2.423038037704636</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-4.135862724291404</v>
       </c>
       <c r="E10">
-        <v>-17.5059337780889</v>
+        <v>-17.21755970296075</v>
       </c>
       <c r="F10">
-        <v>-1.852720881777062</v>
+        <v>-2.346441936091415</v>
       </c>
       <c r="G10">
-        <v>-2.573683222101054</v>
+        <v>-2.090818177740879</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.488898590214737</v>
       </c>
       <c r="E11">
-        <v>-16.7640664051914</v>
+        <v>-17.91029873909685</v>
       </c>
       <c r="F11">
-        <v>-1.521798044767493</v>
+        <v>-1.92754979437415</v>
       </c>
       <c r="G11">
-        <v>-2.352041449293901</v>
+        <v>-1.997139440322552</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-4.810938854757581</v>
       </c>
       <c r="E12">
-        <v>-17.41121564061486</v>
+        <v>-18.35559775092232</v>
       </c>
       <c r="F12">
-        <v>-0.4736887926599602</v>
+        <v>-1.667270957842726</v>
       </c>
       <c r="G12">
-        <v>-2.013130250943121</v>
+        <v>-1.404312444529276</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.069866896917241</v>
       </c>
       <c r="E13">
-        <v>-18.03198783091432</v>
+        <v>-18.58664920334518</v>
       </c>
       <c r="F13">
-        <v>-1.231402254572488</v>
+        <v>-1.612920115810245</v>
       </c>
       <c r="G13">
-        <v>-2.389082693552616</v>
+        <v>-1.183104055324247</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-5.246952884776619</v>
       </c>
       <c r="E14">
-        <v>-18.65118180091036</v>
+        <v>-19.24510763320615</v>
       </c>
       <c r="F14">
-        <v>-0.474768155385808</v>
+        <v>-1.077198349071748</v>
       </c>
       <c r="G14">
-        <v>-2.105495783832118</v>
+        <v>-1.209182783044878</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.33627571019552</v>
       </c>
       <c r="E15">
-        <v>-19.29853454368874</v>
+        <v>-20.19654189634317</v>
       </c>
       <c r="F15">
-        <v>0.01900094423790731</v>
+        <v>-1.23656629696154</v>
       </c>
       <c r="G15">
-        <v>-1.579647440523853</v>
+        <v>-1.551534942766746</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.3494760976774</v>
       </c>
       <c r="E16">
-        <v>-20.20508505203834</v>
+        <v>-19.68977951012156</v>
       </c>
       <c r="F16">
-        <v>-0.02851006814965834</v>
+        <v>-0.7365786432450085</v>
       </c>
       <c r="G16">
-        <v>-1.255654036766695</v>
+        <v>-1.038813423262598</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-5.303537571305804</v>
       </c>
       <c r="E17">
-        <v>-20.04072171385825</v>
+        <v>-21.23731173507725</v>
       </c>
       <c r="F17">
-        <v>0.2504070349447548</v>
+        <v>-0.4434492406207643</v>
       </c>
       <c r="G17">
-        <v>-1.987735538305362</v>
+        <v>-0.9659475417246266</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-5.224348949640842</v>
       </c>
       <c r="E18">
-        <v>-20.96140975355756</v>
+        <v>-20.8292005774543</v>
       </c>
       <c r="F18">
-        <v>0.1215089252321377</v>
+        <v>-0.01274043790256415</v>
       </c>
       <c r="G18">
-        <v>-1.356867383074974</v>
+        <v>-1.730154255456943</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-5.137301667414359</v>
       </c>
       <c r="E19">
-        <v>-21.33603356826842</v>
+        <v>-21.74400351670633</v>
       </c>
       <c r="F19">
-        <v>0.7358576691095575</v>
+        <v>0.5072232957324772</v>
       </c>
       <c r="G19">
-        <v>-0.3717107438521494</v>
+        <v>-1.639976526535299</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-5.060620587972768</v>
       </c>
       <c r="E20">
-        <v>-22.23291540065382</v>
+        <v>-22.5070771866284</v>
       </c>
       <c r="F20">
-        <v>1.022926735814921</v>
+        <v>0.9571609909718622</v>
       </c>
       <c r="G20">
-        <v>-0.9162076357747362</v>
+        <v>-1.425250616150005</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.009622165754407</v>
       </c>
       <c r="E21">
-        <v>-22.88511494104827</v>
+        <v>-23.84596868747001</v>
       </c>
       <c r="F21">
-        <v>1.021013207114454</v>
+        <v>1.469696754106</v>
       </c>
       <c r="G21">
-        <v>-0.9221105292952434</v>
+        <v>-1.829466979702892</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-4.992946806440123</v>
       </c>
       <c r="E22">
-        <v>-23.16822274421654</v>
+        <v>-23.5603772639295</v>
       </c>
       <c r="F22">
-        <v>1.739766064971112</v>
+        <v>1.62260177951915</v>
       </c>
       <c r="G22">
-        <v>-1.461680946174399</v>
+        <v>-2.004251108588745</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-5.010960032164525</v>
       </c>
       <c r="E23">
-        <v>-24.16843647436367</v>
+        <v>-24.38826179657552</v>
       </c>
       <c r="F23">
-        <v>1.852995605259776</v>
+        <v>1.886087226266811</v>
       </c>
       <c r="G23">
-        <v>-1.363148834561193</v>
+        <v>-2.351876972384661</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-5.061746580278875</v>
       </c>
       <c r="E24">
-        <v>-24.34342788032399</v>
+        <v>-24.97364447317613</v>
       </c>
       <c r="F24">
-        <v>1.992340256289098</v>
+        <v>1.692799289967186</v>
       </c>
       <c r="G24">
-        <v>-1.74447680028379</v>
+        <v>-2.467204003952499</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-5.134748603812153</v>
       </c>
       <c r="E25">
-        <v>-23.28185460606385</v>
+        <v>-25.5187908384618</v>
       </c>
       <c r="F25">
-        <v>2.623070793924281</v>
+        <v>2.376986032839826</v>
       </c>
       <c r="G25">
-        <v>-2.634628443836003</v>
+        <v>-3.166927937028909</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-5.218776242334775</v>
       </c>
       <c r="E26">
-        <v>-24.29413756832093</v>
+        <v>-25.09917113225774</v>
       </c>
       <c r="F26">
-        <v>2.175793814782688</v>
+        <v>2.798505755958771</v>
       </c>
       <c r="G26">
-        <v>-2.206275746538273</v>
+        <v>-3.140120811567357</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-5.303144335494272</v>
       </c>
       <c r="E27">
-        <v>-25.08013696475605</v>
+        <v>-26.36436805135159</v>
       </c>
       <c r="F27">
-        <v>2.066684573955548</v>
+        <v>2.552275202211424</v>
       </c>
       <c r="G27">
-        <v>-2.586948415368501</v>
+        <v>-3.321350868848668</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.373478462727612</v>
       </c>
       <c r="E28">
-        <v>-23.97237998056381</v>
+        <v>-25.26348463190194</v>
       </c>
       <c r="F28">
-        <v>2.484310970281336</v>
+        <v>2.460591498069574</v>
       </c>
       <c r="G28">
-        <v>-2.517330300101874</v>
+        <v>-3.484527627282431</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.419129908235787</v>
       </c>
       <c r="E29">
-        <v>-24.36887460611122</v>
+        <v>-25.4006610487497</v>
       </c>
       <c r="F29">
-        <v>2.244755401065746</v>
+        <v>2.631478723062696</v>
       </c>
       <c r="G29">
-        <v>-2.473268763637655</v>
+        <v>-3.495273452019453</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.434460061997829</v>
       </c>
       <c r="E30">
-        <v>-24.19348449186371</v>
+        <v>-25.30478416531603</v>
       </c>
       <c r="F30">
-        <v>2.565331929214349</v>
+        <v>2.316589765501714</v>
       </c>
       <c r="G30">
-        <v>-2.896663656956862</v>
+        <v>-3.368798541047561</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.414662834175886</v>
       </c>
       <c r="E31">
-        <v>-23.39583118445112</v>
+        <v>-25.35624660684198</v>
       </c>
       <c r="F31">
-        <v>2.015733351744156</v>
+        <v>2.248869073588049</v>
       </c>
       <c r="G31">
-        <v>-1.019757598492062</v>
+        <v>-2.994182799668716</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.361454080815358</v>
       </c>
       <c r="E32">
-        <v>-23.43813994821714</v>
+        <v>-24.89307217347445</v>
       </c>
       <c r="F32">
-        <v>1.880008666265068</v>
+        <v>1.843070107039433</v>
       </c>
       <c r="G32">
-        <v>-2.274405737387965</v>
+        <v>-2.772676785580301</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.276723993770543</v>
       </c>
       <c r="E33">
-        <v>-23.71056984506927</v>
+        <v>-23.48380865994496</v>
       </c>
       <c r="F33">
-        <v>2.008804886787141</v>
+        <v>1.737870760353507</v>
       </c>
       <c r="G33">
-        <v>-1.889292192008253</v>
+        <v>-2.74136873644367</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.164690583361185</v>
       </c>
       <c r="E34">
-        <v>-22.6743519259472</v>
+        <v>-23.84733094078455</v>
       </c>
       <c r="F34">
-        <v>1.502536551422584</v>
+        <v>1.677597091391009</v>
       </c>
       <c r="G34">
-        <v>-1.734247902975809</v>
+        <v>-2.465726322513929</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.033423538583571</v>
       </c>
       <c r="E35">
-        <v>-22.12913080285768</v>
+        <v>-23.76761420261579</v>
       </c>
       <c r="F35">
-        <v>2.035662214720706</v>
+        <v>1.533162951038887</v>
       </c>
       <c r="G35">
-        <v>-1.917336810405992</v>
+        <v>-2.465901242401534</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.887196290072411</v>
       </c>
       <c r="E36">
-        <v>-21.42652373661379</v>
+        <v>-22.65020100209332</v>
       </c>
       <c r="F36">
-        <v>1.758545153992577</v>
+        <v>1.508603514280688</v>
       </c>
       <c r="G36">
-        <v>-1.980879723009099</v>
+        <v>-2.482944183092321</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.728854061995911</v>
       </c>
       <c r="E37">
-        <v>-21.65944413413282</v>
+        <v>-22.30913098167575</v>
       </c>
       <c r="F37">
-        <v>1.09570543909008</v>
+        <v>1.334358087836617</v>
       </c>
       <c r="G37">
-        <v>-1.013648456148857</v>
+        <v>-1.987696377136495</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.562202525297228</v>
       </c>
       <c r="E38">
-        <v>-22.2862550936986</v>
+        <v>-22.04857511600131</v>
       </c>
       <c r="F38">
-        <v>1.040685276196136</v>
+        <v>1.17473997299118</v>
       </c>
       <c r="G38">
-        <v>-0.6896889920713831</v>
+        <v>-1.919522003628754</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.385042970421811</v>
       </c>
       <c r="E39">
-        <v>-21.15053869086761</v>
+        <v>-21.09472368387324</v>
       </c>
       <c r="F39">
-        <v>1.878424827790915</v>
+        <v>0.9135872088498026</v>
       </c>
       <c r="G39">
-        <v>-0.9933525276975427</v>
+        <v>-1.126341246424262</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.19825794377847</v>
       </c>
       <c r="E40">
-        <v>-19.09349465379328</v>
+        <v>-20.63615931507627</v>
       </c>
       <c r="F40">
-        <v>0.8957060700929724</v>
+        <v>0.8212408107857138</v>
       </c>
       <c r="G40">
-        <v>-0.8546671642730138</v>
+        <v>-1.068343555332681</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.002097193074491</v>
       </c>
       <c r="E41">
-        <v>-19.3371344897417</v>
+        <v>-20.14765029262729</v>
       </c>
       <c r="F41">
-        <v>1.351193826931114</v>
+        <v>1.006147325703814</v>
       </c>
       <c r="G41">
-        <v>0.07945202893813755</v>
+        <v>-1.267295346898469</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.79535732514478</v>
       </c>
       <c r="E42">
-        <v>-18.82520550863201</v>
+        <v>-20.80384522231622</v>
       </c>
       <c r="F42">
-        <v>1.212740499227205</v>
+        <v>0.6969409685260367</v>
       </c>
       <c r="G42">
-        <v>-0.4222390946685559</v>
+        <v>-1.066983357400711</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.582262062971539</v>
       </c>
       <c r="E43">
-        <v>-17.29478036112329</v>
+        <v>-18.96737823870354</v>
       </c>
       <c r="F43">
-        <v>0.577126735752519</v>
+        <v>0.1950016812085099</v>
       </c>
       <c r="G43">
-        <v>-0.5794999058588558</v>
+        <v>-0.449067106086836</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.364108673141232</v>
       </c>
       <c r="E44">
-        <v>-19.71033375296814</v>
+        <v>-18.98709768607382</v>
       </c>
       <c r="F44">
-        <v>1.256998512823977</v>
+        <v>0.3081666088397559</v>
       </c>
       <c r="G44">
-        <v>-0.4301078788661714</v>
+        <v>-0.7080477480360917</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.144018412388212</v>
       </c>
       <c r="E45">
-        <v>-18.01119685502223</v>
+        <v>-19.19036000152225</v>
       </c>
       <c r="F45">
-        <v>0.5409974914794186</v>
+        <v>0.1684127443134513</v>
       </c>
       <c r="G45">
-        <v>-0.1366210256561713</v>
+        <v>-0.5725657682248588</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.930132088760565</v>
       </c>
       <c r="E46">
-        <v>-17.41604582538563</v>
+        <v>-18.93112485704911</v>
       </c>
       <c r="F46">
-        <v>0.8367047734611749</v>
+        <v>0.4156771005794926</v>
       </c>
       <c r="G46">
-        <v>-0.501080970575586</v>
+        <v>-0.9131556753477248</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.726479703697935</v>
       </c>
       <c r="E47">
-        <v>-16.79028978149636</v>
+        <v>-18.46142572869027</v>
       </c>
       <c r="F47">
-        <v>0.7018258511003453</v>
+        <v>0.1518868146276012</v>
       </c>
       <c r="G47">
-        <v>0.2998197583848278</v>
+        <v>-1.317116185930683</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.540209027950535</v>
       </c>
       <c r="E48">
-        <v>-16.58984334332616</v>
+        <v>-17.3628141158353</v>
       </c>
       <c r="F48">
-        <v>0.7521152077569006</v>
+        <v>0.06310073966074459</v>
       </c>
       <c r="G48">
-        <v>-0.1021226466292004</v>
+        <v>-1.314852670370188</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.376262052822008</v>
       </c>
       <c r="E49">
-        <v>-16.36019982954242</v>
+        <v>-17.33013664913155</v>
       </c>
       <c r="F49">
-        <v>1.045768138579714</v>
+        <v>-0.03185667245696834</v>
       </c>
       <c r="G49">
-        <v>-1.056707466690089</v>
+        <v>-1.510966582565436</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.237195574959342</v>
       </c>
       <c r="E50">
-        <v>-16.6126652395561</v>
+        <v>-16.35811907066868</v>
       </c>
       <c r="F50">
-        <v>0.6997143425906095</v>
+        <v>-0.2317276445066415</v>
       </c>
       <c r="G50">
-        <v>-1.241553405230092</v>
+        <v>-1.124816571583052</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.128161241437506</v>
       </c>
       <c r="E51">
-        <v>-14.75250833854659</v>
+        <v>-17.04382256682052</v>
       </c>
       <c r="F51">
-        <v>0.7055998929874999</v>
+        <v>-0.2101246510090332</v>
       </c>
       <c r="G51">
-        <v>-0.456165720630073</v>
+        <v>-1.347659286902118</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.049631227832298</v>
       </c>
       <c r="E52">
-        <v>-16.09621756452499</v>
+        <v>-15.65532510991517</v>
       </c>
       <c r="F52">
-        <v>0.625826455363102</v>
+        <v>-0.4180713768685986</v>
       </c>
       <c r="G52">
-        <v>-0.9507321222476183</v>
+        <v>-1.230810191237661</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.002270068757946</v>
       </c>
       <c r="E53">
-        <v>-15.16437815241851</v>
+        <v>-16.74123620253881</v>
       </c>
       <c r="F53">
-        <v>0.8433996388106005</v>
+        <v>-0.6533285476310611</v>
       </c>
       <c r="G53">
-        <v>-1.284223414827247</v>
+        <v>-1.439351247686607</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-1.986236907539745</v>
       </c>
       <c r="E54">
-        <v>-14.46549651673299</v>
+        <v>-15.86899537294362</v>
       </c>
       <c r="F54">
-        <v>0.660221926662143</v>
+        <v>-0.5848349889305839</v>
       </c>
       <c r="G54">
-        <v>-1.49181677098962</v>
+        <v>-1.244096270461836</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-1.998641522062116</v>
       </c>
       <c r="E55">
-        <v>-13.96235157757531</v>
+        <v>-16.47385661065768</v>
       </c>
       <c r="F55">
-        <v>0.196141514754762</v>
+        <v>-0.6787262922008939</v>
       </c>
       <c r="G55">
-        <v>-1.68615276611832</v>
+        <v>-1.716554886881834</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-2.037362509557021</v>
       </c>
       <c r="E56">
-        <v>-13.91600173919022</v>
+        <v>-15.01610850812213</v>
       </c>
       <c r="F56">
-        <v>0.3181020474689332</v>
+        <v>-0.8392034240430337</v>
       </c>
       <c r="G56">
-        <v>-1.913606056385291</v>
+        <v>-1.857352342680574</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-2.096777224612744</v>
       </c>
       <c r="E57">
-        <v>-13.44430906939547</v>
+        <v>-15.79445768929692</v>
       </c>
       <c r="F57">
-        <v>0.07411471264836682</v>
+        <v>-0.9303238383509793</v>
       </c>
       <c r="G57">
-        <v>-1.807249543232518</v>
+        <v>-1.953278931191849</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-2.172415783077544</v>
       </c>
       <c r="E58">
-        <v>-14.09866827967883</v>
+        <v>-15.9204287419903</v>
       </c>
       <c r="F58">
-        <v>0.0987677549230829</v>
+        <v>-0.7561985251803148</v>
       </c>
       <c r="G58">
-        <v>-1.347531360417153</v>
+        <v>-1.944297969798419</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-2.260806472613535</v>
       </c>
       <c r="E59">
-        <v>-13.18911499954138</v>
+        <v>-15.89692571910309</v>
       </c>
       <c r="F59">
-        <v>-0.6002674736447386</v>
+        <v>-1.127786746360714</v>
       </c>
       <c r="G59">
-        <v>-2.459632844638271</v>
+        <v>-1.408735045866622</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-2.35682297020512</v>
       </c>
       <c r="E60">
-        <v>-14.32197399298089</v>
+        <v>-15.75197449065525</v>
       </c>
       <c r="F60">
-        <v>-0.8425359461044961</v>
+        <v>-1.353476273620842</v>
       </c>
       <c r="G60">
-        <v>-2.722529603474196</v>
+        <v>-1.518075640087038</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-2.458108282286787</v>
       </c>
       <c r="E61">
-        <v>-11.3846152834959</v>
+        <v>-15.77573916585592</v>
       </c>
       <c r="F61">
-        <v>-0.4979980624625145</v>
+        <v>-1.143258992710203</v>
       </c>
       <c r="G61">
-        <v>-2.818683326764899</v>
+        <v>-2.25732102478372</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-2.560892461376259</v>
       </c>
       <c r="E62">
-        <v>-15.49086209466328</v>
+        <v>-14.87958414545237</v>
       </c>
       <c r="F62">
-        <v>-0.4935696103271484</v>
+        <v>-1.449178388033672</v>
       </c>
       <c r="G62">
-        <v>-2.377645021498949</v>
+        <v>-2.146058922544245</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-2.664132549019921</v>
       </c>
       <c r="E63">
-        <v>-13.25662129641514</v>
+        <v>-15.33766674173566</v>
       </c>
       <c r="F63">
-        <v>-0.1685066443249832</v>
+        <v>-1.520326864260122</v>
       </c>
       <c r="G63">
-        <v>-2.716778133139974</v>
+        <v>-1.615725320028448</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-2.76851985298817</v>
       </c>
       <c r="E64">
-        <v>-12.90052911063567</v>
+        <v>-15.15325585249062</v>
       </c>
       <c r="F64">
-        <v>-0.382855821840786</v>
+        <v>-1.705556442465313</v>
       </c>
       <c r="G64">
-        <v>-2.956950971054849</v>
+        <v>-1.765924067099786</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.872724422486867</v>
       </c>
       <c r="E65">
-        <v>-12.39870904589061</v>
+        <v>-14.39878348322227</v>
       </c>
       <c r="F65">
-        <v>-0.7806875507092766</v>
+        <v>-1.713245348698099</v>
       </c>
       <c r="G65">
-        <v>-2.552982628238117</v>
+        <v>-1.959779685223721</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.978956074904811</v>
       </c>
       <c r="E66">
-        <v>-12.1186372402008</v>
+        <v>-15.98141449708408</v>
       </c>
       <c r="F66">
-        <v>-0.8481290828081983</v>
+        <v>-1.726606086537852</v>
       </c>
       <c r="G66">
-        <v>-2.517121440534585</v>
+        <v>-2.165146076249874</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-3.088504072544809</v>
       </c>
       <c r="E67">
-        <v>-13.01821035352469</v>
+        <v>-15.18379026215076</v>
       </c>
       <c r="F67">
-        <v>-0.8204906044137928</v>
+        <v>-2.229728282506576</v>
       </c>
       <c r="G67">
-        <v>-2.201255284689562</v>
+        <v>-1.892931569968265</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-3.20111459398785</v>
       </c>
       <c r="E68">
-        <v>-13.42265007233649</v>
+        <v>-15.22011424839771</v>
       </c>
       <c r="F68">
-        <v>-1.142095964876673</v>
+        <v>-2.146461619544572</v>
       </c>
       <c r="G68">
-        <v>-2.765653882630206</v>
+        <v>-1.609874641399763</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-3.318784015846911</v>
       </c>
       <c r="E69">
-        <v>-13.02654584865362</v>
+        <v>-14.96101200668696</v>
       </c>
       <c r="F69">
-        <v>-1.032715847908818</v>
+        <v>-2.21596412974166</v>
       </c>
       <c r="G69">
-        <v>-2.091392541550924</v>
+        <v>-1.704253058368508</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-3.43908363710956</v>
       </c>
       <c r="E70">
-        <v>-13.47644661862699</v>
+        <v>-15.14351241872257</v>
       </c>
       <c r="F70">
-        <v>-0.9925466558122642</v>
+        <v>-2.115464939699218</v>
       </c>
       <c r="G70">
-        <v>-3.084535448477964</v>
+        <v>-2.334411091070113</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.561249707312636</v>
       </c>
       <c r="E71">
-        <v>-14.45374708189505</v>
+        <v>-15.03904254105784</v>
       </c>
       <c r="F71">
-        <v>-1.193951764291922</v>
+        <v>-2.119324303428861</v>
       </c>
       <c r="G71">
-        <v>-1.338239720417381</v>
+        <v>-1.786389693949523</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.683938680372456</v>
       </c>
       <c r="E72">
-        <v>-13.10321412970995</v>
+        <v>-15.78131692866517</v>
       </c>
       <c r="F72">
-        <v>-0.9545204501867529</v>
+        <v>-2.516038564670975</v>
       </c>
       <c r="G72">
-        <v>-2.274476227491925</v>
+        <v>-1.488665602268146</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.802015433091527</v>
       </c>
       <c r="E73">
-        <v>-14.6620970812164</v>
+        <v>-15.2822545962398</v>
       </c>
       <c r="F73">
-        <v>-1.465174990949133</v>
+        <v>-2.351277944988959</v>
       </c>
       <c r="G73">
-        <v>-1.663896168479079</v>
+        <v>-1.617218665934565</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.914042395885575</v>
       </c>
       <c r="E74">
-        <v>-13.10944809990852</v>
+        <v>-15.97152154770834</v>
       </c>
       <c r="F74">
-        <v>-1.558010125780874</v>
+        <v>-2.588627571810893</v>
       </c>
       <c r="G74">
-        <v>-3.32599799422085</v>
+        <v>-2.041396782631105</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.018582404907256</v>
       </c>
       <c r="E75">
-        <v>-13.65870614440577</v>
+        <v>-16.12082118841328</v>
       </c>
       <c r="F75">
-        <v>-1.586636846486819</v>
+        <v>-2.435757337828661</v>
       </c>
       <c r="G75">
-        <v>-2.287075680888638</v>
+        <v>-1.690118487152221</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.113397008019841</v>
       </c>
       <c r="E76">
-        <v>-15.38853527404216</v>
+        <v>-16.6931420153973</v>
       </c>
       <c r="F76">
-        <v>-1.250079454403408</v>
+        <v>-2.194097715409961</v>
       </c>
       <c r="G76">
-        <v>-1.653917902651844</v>
+        <v>-1.761073303649498</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.199746815650728</v>
       </c>
       <c r="E77">
-        <v>-14.24556321102669</v>
+        <v>-16.62156972463653</v>
       </c>
       <c r="F77">
-        <v>-1.552370600502615</v>
+        <v>-2.327566756451226</v>
       </c>
       <c r="G77">
-        <v>-2.18832948821896</v>
+        <v>-0.9885304824377564</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.275676667440385</v>
       </c>
       <c r="E78">
-        <v>-16.33211581456393</v>
+        <v>-17.69527037596518</v>
       </c>
       <c r="F78">
-        <v>-1.561424656215213</v>
+        <v>-2.304305371413213</v>
       </c>
       <c r="G78">
-        <v>-1.930505406123568</v>
+        <v>-1.113519879737305</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.342876082321356</v>
       </c>
       <c r="E79">
-        <v>-15.89271020960839</v>
+        <v>-17.58138932143838</v>
       </c>
       <c r="F79">
-        <v>-1.850804867974387</v>
+        <v>-2.190904359072169</v>
       </c>
       <c r="G79">
-        <v>-0.8701749871442268</v>
+        <v>-0.9464035077155525</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.404178347782691</v>
       </c>
       <c r="E80">
-        <v>-15.60310263071677</v>
+        <v>-19.15383666113171</v>
       </c>
       <c r="F80">
-        <v>-1.538510357118974</v>
+        <v>-2.494015588900147</v>
       </c>
       <c r="G80">
-        <v>-1.185571208962849</v>
+        <v>-1.167525742349074</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.45904995783776</v>
       </c>
       <c r="E81">
-        <v>-16.92217916032762</v>
+        <v>-19.48796666542549</v>
       </c>
       <c r="F81">
-        <v>-1.365012946439631</v>
+        <v>-2.509863085683105</v>
       </c>
       <c r="G81">
-        <v>-0.7374499536212096</v>
+        <v>-0.7132483512615894</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.511125716460739</v>
       </c>
       <c r="E82">
-        <v>-19.35592361777522</v>
+        <v>-20.63573153430981</v>
       </c>
       <c r="F82">
-        <v>-1.205696357328813</v>
+        <v>-2.196724468444238</v>
       </c>
       <c r="G82">
-        <v>-0.8809782482622536</v>
+        <v>-1.219330747270535</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.563971333363726</v>
       </c>
       <c r="E83">
-        <v>-19.95512818166486</v>
+        <v>-22.03348649925821</v>
       </c>
       <c r="F83">
-        <v>-1.93331688823244</v>
+        <v>-1.976155080100814</v>
       </c>
       <c r="G83">
-        <v>-0.3738411114384978</v>
+        <v>-0.4751693305087866</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-4.619956474302063</v>
       </c>
       <c r="E84">
-        <v>-20.18106703094686</v>
+        <v>-22.63939849943744</v>
       </c>
       <c r="F84">
-        <v>-2.048759826221385</v>
+        <v>-2.368033332445385</v>
       </c>
       <c r="G84">
-        <v>-0.6477317157476015</v>
+        <v>-0.4749735246644531</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-4.686640095039488</v>
       </c>
       <c r="E85">
-        <v>-20.90270411148111</v>
+        <v>-23.44977724634931</v>
       </c>
       <c r="F85">
-        <v>-1.69507179624808</v>
+        <v>-2.496547908050506</v>
       </c>
       <c r="G85">
-        <v>-0.3539080764853479</v>
+        <v>-0.02475061992696703</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-4.766024197666672</v>
       </c>
       <c r="E86">
-        <v>-21.99969181870808</v>
+        <v>-24.73808678646582</v>
       </c>
       <c r="F86">
-        <v>-2.129052650207338</v>
+        <v>-2.019355268524211</v>
       </c>
       <c r="G86">
-        <v>-0.1116518643867639</v>
+        <v>0.2841291833922369</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-4.866271353963742</v>
       </c>
       <c r="E87">
-        <v>-23.09491856433331</v>
+        <v>-26.28685666839631</v>
       </c>
       <c r="F87">
-        <v>-1.522478962772595</v>
+        <v>-2.06355032619837</v>
       </c>
       <c r="G87">
-        <v>-0.4474797733754391</v>
+        <v>0.05834154817439552</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.995431508659808</v>
       </c>
       <c r="E88">
-        <v>-24.20627222953286</v>
+        <v>-27.10122665139134</v>
       </c>
       <c r="F88">
-        <v>-1.502874819817942</v>
+        <v>-1.992873191024114</v>
       </c>
       <c r="G88">
-        <v>-0.9828677774196317</v>
+        <v>-0.1749833066779899</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-5.155771925302147</v>
       </c>
       <c r="E89">
-        <v>-26.23193875504811</v>
+        <v>-29.488878769556</v>
       </c>
       <c r="F89">
-        <v>-1.637133294994074</v>
+        <v>-1.909545228874303</v>
       </c>
       <c r="G89">
-        <v>-0.2096017799561521</v>
+        <v>0.06924923907606682</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-5.356328832166983</v>
       </c>
       <c r="E90">
-        <v>-29.09213702793476</v>
+        <v>-29.99925860284153</v>
       </c>
       <c r="F90">
-        <v>-1.637581441758989</v>
+        <v>-1.798480212609154</v>
       </c>
       <c r="G90">
-        <v>0.4570753480859454</v>
+        <v>-0.215590828048166</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.602533003148408</v>
       </c>
       <c r="E91">
-        <v>-30.77059301008869</v>
+        <v>-31.88933316162944</v>
       </c>
       <c r="F91">
-        <v>-1.895535879358158</v>
+        <v>-1.993639430871703</v>
       </c>
       <c r="G91">
-        <v>0.3393307670267363</v>
+        <v>0.2223667986002699</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.898054896512079</v>
       </c>
       <c r="E92">
-        <v>-32.50230977427221</v>
+        <v>-33.21809498004978</v>
       </c>
       <c r="F92">
-        <v>-1.254636303486208</v>
+        <v>-1.44325970294067</v>
       </c>
       <c r="G92">
-        <v>0.321394951685788</v>
+        <v>-0.06903668042602169</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.252260178912469</v>
       </c>
       <c r="E93">
-        <v>-33.94575837021637</v>
+        <v>-35.89346496595326</v>
       </c>
       <c r="F93">
-        <v>-1.50031185107368</v>
+        <v>-1.429779680194913</v>
       </c>
       <c r="G93">
-        <v>-0.001919658477681342</v>
+        <v>-0.3993141464139902</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.660764771796774</v>
       </c>
       <c r="E94">
-        <v>-34.25662208466846</v>
+        <v>-37.42964854096385</v>
       </c>
       <c r="F94">
-        <v>-1.517839276949515</v>
+        <v>-1.52451343311387</v>
       </c>
       <c r="G94">
-        <v>0.2339506723510396</v>
+        <v>-0.7919492469606993</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-7.127780762108447</v>
       </c>
       <c r="E95">
-        <v>-38.19528889548467</v>
+        <v>-39.83720700100841</v>
       </c>
       <c r="F95">
-        <v>-1.637261691941508</v>
+        <v>-1.709938506026123</v>
       </c>
       <c r="G95">
-        <v>-0.4146000559949584</v>
+        <v>-1.072787042626756</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-7.655827857102873</v>
       </c>
       <c r="E96">
-        <v>-39.52205301925777</v>
+        <v>-41.49830255982454</v>
       </c>
       <c r="F96">
-        <v>-2.008257630428906</v>
+        <v>-1.712402070682049</v>
       </c>
       <c r="G96">
-        <v>-1.265125818143253</v>
+        <v>-0.9775392477091696</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-8.227055541088564</v>
       </c>
       <c r="E97">
-        <v>-42.42467426922189</v>
+        <v>-44.10525877217979</v>
       </c>
       <c r="F97">
-        <v>-1.362120287469055</v>
+        <v>-1.551279640633128</v>
       </c>
       <c r="G97">
-        <v>-0.94742953033986</v>
+        <v>-0.8078173525854859</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-8.847552584844314</v>
       </c>
       <c r="E98">
-        <v>-44.0989978061076</v>
+        <v>-45.61765275272176</v>
       </c>
       <c r="F98">
-        <v>-1.700595350089947</v>
+        <v>-1.682721666639742</v>
       </c>
       <c r="G98">
-        <v>-1.403458731047982</v>
+        <v>-0.9897314249496686</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-9.485584714658582</v>
       </c>
       <c r="E99">
-        <v>-46.79267203262243</v>
+        <v>-47.65350606731398</v>
       </c>
       <c r="F99">
-        <v>-1.826233834072548</v>
+        <v>-1.391805661715778</v>
       </c>
       <c r="G99">
-        <v>-1.805643935308984</v>
+        <v>-1.373991256848087</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-10.15238879969507</v>
       </c>
       <c r="E100">
-        <v>-48.14011811049035</v>
+        <v>-49.95972513272989</v>
       </c>
       <c r="F100">
-        <v>-2.129094068577478</v>
+        <v>-1.552000320273563</v>
       </c>
       <c r="G100">
-        <v>-1.502411172540358</v>
+        <v>-1.619518731919335</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-10.79173094252282</v>
       </c>
       <c r="E101">
-        <v>-50.78964266231942</v>
+        <v>-51.51248105922939</v>
       </c>
       <c r="F101">
-        <v>-2.264985255904529</v>
+        <v>-1.553099563817078</v>
       </c>
       <c r="G101">
-        <v>-2.319561175835861</v>
+        <v>-1.748160560901851</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-11.45317485408265</v>
       </c>
       <c r="E102">
-        <v>-50.96612714775102</v>
+        <v>-53.31472661982831</v>
       </c>
       <c r="F102">
-        <v>-1.891147188858126</v>
+        <v>-1.717243049784009</v>
       </c>
       <c r="G102">
-        <v>-2.09937880925514</v>
+        <v>-2.342188499207039</v>
       </c>
     </row>
   </sheetData>
